--- a/Bharat.xlsx
+++ b/Bharat.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">bharat </t>
   </si>
@@ -31,6 +31,9 @@
   </si>
   <si>
     <t>this sis sc lknlkv</t>
+  </si>
+  <si>
+    <t>dsfdgfhgjhrfdgfhg</t>
   </si>
 </sst>
 </file>
@@ -390,9 +393,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I17" t="s">
         <v>3</v>
+      </c>
+      <c r="J17" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Bharat.xlsx
+++ b/Bharat.xlsx
@@ -33,7 +33,7 @@
     <t>this sis sc lknlkv</t>
   </si>
   <si>
-    <t>dsfdgfhgjhrfdgfhg</t>
+    <t>Bharat Purobhit</t>
   </si>
 </sst>
 </file>
